--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/188.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/188.xlsx
@@ -426,13 +426,13 @@
         <v>4.55424596688535</v>
       </c>
       <c r="E2">
-        <v>-17.2745862063334</v>
+        <v>-16.95970329468405</v>
       </c>
       <c r="F2">
-        <v>-3.644627023430091</v>
+        <v>-3.437752204989748</v>
       </c>
       <c r="G2">
-        <v>-11.7388612678245</v>
+        <v>-11.44876809385478</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>4.439874314068049</v>
       </c>
       <c r="E3">
-        <v>-17.3373463276057</v>
+        <v>-17.37005549536311</v>
       </c>
       <c r="F3">
-        <v>-3.389886651353784</v>
+        <v>-3.180058703122461</v>
       </c>
       <c r="G3">
-        <v>-10.61662605655803</v>
+        <v>-12.17215871018647</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>4.292576170509562</v>
       </c>
       <c r="E4">
-        <v>-16.74608611879422</v>
+        <v>-17.4333997897824</v>
       </c>
       <c r="F4">
-        <v>-3.429890998337181</v>
+        <v>-3.240761466399609</v>
       </c>
       <c r="G4">
-        <v>-10.84446442166176</v>
+        <v>-11.23767115754315</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>4.136070295728478</v>
       </c>
       <c r="E5">
-        <v>-16.65796201460496</v>
+        <v>-18.55221363506545</v>
       </c>
       <c r="F5">
-        <v>-3.411109424213508</v>
+        <v>-2.878484094826676</v>
       </c>
       <c r="G5">
-        <v>-10.58381192917278</v>
+        <v>-11.50877173175407</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>3.983792703577754</v>
       </c>
       <c r="E6">
-        <v>-19.35853560297521</v>
+        <v>-18.68036039253451</v>
       </c>
       <c r="F6">
-        <v>-3.976464378052351</v>
+        <v>-3.214289329308345</v>
       </c>
       <c r="G6">
-        <v>-10.90574924068475</v>
+        <v>-11.04450413587222</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>3.856133925915091</v>
       </c>
       <c r="E7">
-        <v>-18.38034898952635</v>
+        <v>-19.28121190929424</v>
       </c>
       <c r="F7">
-        <v>-3.378598488755836</v>
+        <v>-2.963778601190733</v>
       </c>
       <c r="G7">
-        <v>-10.57757817192233</v>
+        <v>-11.99272383141243</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>3.769535972313814</v>
       </c>
       <c r="E8">
-        <v>-18.72213103678126</v>
+        <v>-20.17012418615588</v>
       </c>
       <c r="F8">
-        <v>-3.923960795328113</v>
+        <v>-2.866308750740329</v>
       </c>
       <c r="G8">
-        <v>-10.1834411727444</v>
+        <v>-10.66093770860118</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>3.733417147780561</v>
       </c>
       <c r="E9">
-        <v>-20.85519626251026</v>
+        <v>-20.24467192527015</v>
       </c>
       <c r="F9">
-        <v>-3.184184801155806</v>
+        <v>-3.006866960014752</v>
       </c>
       <c r="G9">
-        <v>-9.131214067996908</v>
+        <v>-10.55736729140508</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>3.749807591118828</v>
       </c>
       <c r="E10">
-        <v>-20.73714800207831</v>
+        <v>-20.4463746860458</v>
       </c>
       <c r="F10">
-        <v>-3.671453701769753</v>
+        <v>-2.801030085930117</v>
       </c>
       <c r="G10">
-        <v>-9.66960808904858</v>
+        <v>-11.33633534625005</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>3.82259276477624</v>
       </c>
       <c r="E11">
-        <v>-20.59662492514629</v>
+        <v>-21.32140719007393</v>
       </c>
       <c r="F11">
-        <v>-3.266136016682164</v>
+        <v>-2.520264066792655</v>
       </c>
       <c r="G11">
-        <v>-7.961389764603423</v>
+        <v>-10.85719015871472</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>3.944521031147234</v>
       </c>
       <c r="E12">
-        <v>-20.79461433723565</v>
+        <v>-21.57303637678414</v>
       </c>
       <c r="F12">
-        <v>-3.685245190658962</v>
+        <v>-2.795183468801158</v>
       </c>
       <c r="G12">
-        <v>-9.641418793781687</v>
+        <v>-10.18069341994681</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>4.098446289104647</v>
       </c>
       <c r="E13">
-        <v>-21.79187488320481</v>
+        <v>-23.6529418461371</v>
       </c>
       <c r="F13">
-        <v>-3.172030994621931</v>
+        <v>-2.496059999650257</v>
       </c>
       <c r="G13">
-        <v>-9.23458916300619</v>
+        <v>-10.06416883805554</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>4.274389994574701</v>
       </c>
       <c r="E14">
-        <v>-22.41894173599494</v>
+        <v>-23.06809848499449</v>
       </c>
       <c r="F14">
-        <v>-2.833165770954321</v>
+        <v>-2.344758693528927</v>
       </c>
       <c r="G14">
-        <v>-9.668230902104243</v>
+        <v>-8.647881040354394</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>4.456898508627225</v>
       </c>
       <c r="E15">
-        <v>-23.09471685521157</v>
+        <v>-23.82944817753406</v>
       </c>
       <c r="F15">
-        <v>-2.236583851132145</v>
+        <v>-2.251240983957279</v>
       </c>
       <c r="G15">
-        <v>-9.808919155886651</v>
+        <v>-9.021082149541973</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>4.627040330222533</v>
       </c>
       <c r="E16">
-        <v>-23.91866364395918</v>
+        <v>-24.34651839667788</v>
       </c>
       <c r="F16">
-        <v>-2.647893946011586</v>
+        <v>-2.27044502545638</v>
       </c>
       <c r="G16">
-        <v>-8.635456562945508</v>
+        <v>-8.893506966640619</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>4.770311900554104</v>
       </c>
       <c r="E17">
-        <v>-23.61584911554027</v>
+        <v>-25.35745493415021</v>
       </c>
       <c r="F17">
-        <v>-1.78087326346265</v>
+        <v>-1.506612413539373</v>
       </c>
       <c r="G17">
-        <v>-6.919355829571345</v>
+        <v>-8.388728224994704</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.875199950266994</v>
       </c>
       <c r="E18">
-        <v>-26.24230969830099</v>
+        <v>-25.33956746181991</v>
       </c>
       <c r="F18">
-        <v>-2.303022230306277</v>
+        <v>-1.844119943033795</v>
       </c>
       <c r="G18">
-        <v>-7.167514323195114</v>
+        <v>-8.75718532242451</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.928678139191946</v>
       </c>
       <c r="E19">
-        <v>-25.83091142012616</v>
+        <v>-25.95799851467742</v>
       </c>
       <c r="F19">
-        <v>-1.49274885668612</v>
+        <v>-1.364061152293814</v>
       </c>
       <c r="G19">
-        <v>-7.935802558130396</v>
+        <v>-8.566425067360624</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>4.918913378804207</v>
       </c>
       <c r="E20">
-        <v>-26.6639106284151</v>
+        <v>-26.0118873553687</v>
       </c>
       <c r="F20">
-        <v>-1.703141751486153</v>
+        <v>-1.129830328743421</v>
       </c>
       <c r="G20">
-        <v>-6.982775950467164</v>
+        <v>-8.273547724592381</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.843145108552195</v>
       </c>
       <c r="E21">
-        <v>-28.63626484008588</v>
+        <v>-27.11850149167509</v>
       </c>
       <c r="F21">
-        <v>-1.587769224726446</v>
+        <v>-1.05917555948904</v>
       </c>
       <c r="G21">
-        <v>-8.805095537468842</v>
+        <v>-7.586050042997473</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.699115651843286</v>
       </c>
       <c r="E22">
-        <v>-25.71371904128166</v>
+        <v>-27.05644781234798</v>
       </c>
       <c r="F22">
-        <v>-1.493350251420553</v>
+        <v>-1.028122550660294</v>
       </c>
       <c r="G22">
-        <v>-7.465417074091971</v>
+        <v>-7.815878045970297</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.486770794724296</v>
       </c>
       <c r="E23">
-        <v>-26.61920553301137</v>
+        <v>-28.27833425451962</v>
       </c>
       <c r="F23">
-        <v>-1.340436113965973</v>
+        <v>-0.8091618518131068</v>
       </c>
       <c r="G23">
-        <v>-7.280278125353769</v>
+        <v>-7.996882123329949</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.21668629749299</v>
       </c>
       <c r="E24">
-        <v>-28.779206122138</v>
+        <v>-28.3362398516557</v>
       </c>
       <c r="F24">
-        <v>-0.9810779091205051</v>
+        <v>-0.7985860851815655</v>
       </c>
       <c r="G24">
-        <v>-7.663198996244649</v>
+        <v>-7.557814400093029</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.900003236594095</v>
       </c>
       <c r="E25">
-        <v>-28.19710701624403</v>
+        <v>-28.41820523119453</v>
       </c>
       <c r="F25">
-        <v>-1.270457292512276</v>
+        <v>-0.5361203587067506</v>
       </c>
       <c r="G25">
-        <v>-7.719335916954071</v>
+        <v>-7.86783043711808</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.547772137955318</v>
       </c>
       <c r="E26">
-        <v>-26.72061165146514</v>
+        <v>-28.65532065871016</v>
       </c>
       <c r="F26">
-        <v>-0.9528637153811539</v>
+        <v>-0.8006810263432454</v>
       </c>
       <c r="G26">
-        <v>-8.23572143126067</v>
+        <v>-8.44275632819561</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.175523597317945</v>
       </c>
       <c r="E27">
-        <v>-29.47967501011846</v>
+        <v>-29.68939996259869</v>
       </c>
       <c r="F27">
-        <v>-0.6172705429546014</v>
+        <v>-0.6403695679816656</v>
       </c>
       <c r="G27">
-        <v>-8.768732505265488</v>
+        <v>-8.005939775925395</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.800093984601437</v>
       </c>
       <c r="E28">
-        <v>-27.94784622143984</v>
+        <v>-28.46296919676035</v>
       </c>
       <c r="F28">
-        <v>-0.2827517630494798</v>
+        <v>-0.8559861476237517</v>
       </c>
       <c r="G28">
-        <v>-7.411769683628081</v>
+        <v>-8.068042299696584</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.434790121372076</v>
       </c>
       <c r="E29">
-        <v>-27.33138958324968</v>
+        <v>-27.72741369216847</v>
       </c>
       <c r="F29">
-        <v>-1.190138789136836</v>
+        <v>-0.3884829216080031</v>
       </c>
       <c r="G29">
-        <v>-8.675044066504112</v>
+        <v>-8.07772895594449</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.090697296909904</v>
       </c>
       <c r="E30">
-        <v>-26.95474734308372</v>
+        <v>-28.02636090378482</v>
       </c>
       <c r="F30">
-        <v>-0.7904556591230883</v>
+        <v>-0.5183452509774787</v>
       </c>
       <c r="G30">
-        <v>-8.21573235729455</v>
+        <v>-8.67850689713819</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.783559724487091</v>
       </c>
       <c r="E31">
-        <v>-27.0033831539261</v>
+        <v>-28.63251526360753</v>
       </c>
       <c r="F31">
-        <v>-0.867210525931685</v>
+        <v>-0.38758248624116</v>
       </c>
       <c r="G31">
-        <v>-8.275630057736583</v>
+        <v>-9.137116770693428</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.523182721452373</v>
       </c>
       <c r="E32">
-        <v>-26.57865304827268</v>
+        <v>-27.65351352483729</v>
       </c>
       <c r="F32">
-        <v>-0.9574379601794127</v>
+        <v>-0.4496454287937046</v>
       </c>
       <c r="G32">
-        <v>-7.817493592193461</v>
+        <v>-8.501561548609684</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.314307171996029</v>
       </c>
       <c r="E33">
-        <v>-26.41301052602012</v>
+        <v>-27.10254314927205</v>
       </c>
       <c r="F33">
-        <v>-0.8722768209672067</v>
+        <v>-0.751541443641776</v>
       </c>
       <c r="G33">
-        <v>-8.170238840493885</v>
+        <v>-7.78484168153963</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.164750463251996</v>
       </c>
       <c r="E34">
-        <v>-27.4946455997002</v>
+        <v>-26.96591003151262</v>
       </c>
       <c r="F34">
-        <v>-0.930168105279253</v>
+        <v>-0.7945254281730424</v>
       </c>
       <c r="G34">
-        <v>-8.548031676344435</v>
+        <v>-7.461811889999704</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.077660285528978</v>
       </c>
       <c r="E35">
-        <v>-26.99481980957759</v>
+        <v>-26.35229274652528</v>
       </c>
       <c r="F35">
-        <v>-0.7204461880754882</v>
+        <v>-0.885220061635949</v>
       </c>
       <c r="G35">
-        <v>-7.824353042550832</v>
+        <v>-8.098820441575187</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.050868353887484</v>
       </c>
       <c r="E36">
-        <v>-25.47971920388331</v>
+        <v>-27.08379979535431</v>
       </c>
       <c r="F36">
-        <v>-0.8764385387988715</v>
+        <v>-0.9766751363746257</v>
       </c>
       <c r="G36">
-        <v>-7.50879846283858</v>
+        <v>-7.911509774963224</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.08043955970516</v>
       </c>
       <c r="E37">
-        <v>-26.76503598148038</v>
+        <v>-25.72773013986139</v>
       </c>
       <c r="F37">
-        <v>-1.403843496813261</v>
+        <v>-0.9090024897703228</v>
       </c>
       <c r="G37">
-        <v>-8.471882507850118</v>
+        <v>-7.607032280625375</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.163430630310326</v>
       </c>
       <c r="E38">
-        <v>-23.95883120840722</v>
+        <v>-24.86129267949981</v>
       </c>
       <c r="F38">
-        <v>-0.5395539415913545</v>
+        <v>-1.071932417492152</v>
       </c>
       <c r="G38">
-        <v>-7.984844979749159</v>
+        <v>-7.284803641105952</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.291998646144969</v>
       </c>
       <c r="E39">
-        <v>-24.79684796589665</v>
+        <v>-24.87337917662628</v>
       </c>
       <c r="F39">
-        <v>-0.2647389138756046</v>
+        <v>-0.9278925800237627</v>
       </c>
       <c r="G39">
-        <v>-7.468800451633106</v>
+        <v>-7.132293429202807</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.454246051669623</v>
       </c>
       <c r="E40">
-        <v>-23.51019981694132</v>
+        <v>-24.87585172343447</v>
       </c>
       <c r="F40">
-        <v>-1.154751762056644</v>
+        <v>-0.6700897336593062</v>
       </c>
       <c r="G40">
-        <v>-7.788708398729499</v>
+        <v>-7.612524475675025</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.642900527225269</v>
       </c>
       <c r="E41">
-        <v>-23.8225603685684</v>
+        <v>-24.58159601089006</v>
       </c>
       <c r="F41">
-        <v>-0.6753515234018886</v>
+        <v>-0.6419492646188042</v>
       </c>
       <c r="G41">
-        <v>-5.861745777776997</v>
+        <v>-7.455300046923958</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.847592415343447</v>
       </c>
       <c r="E42">
-        <v>-25.05502532602195</v>
+        <v>-24.39206125977302</v>
       </c>
       <c r="F42">
-        <v>-1.005532143218549</v>
+        <v>-1.15505825799568</v>
       </c>
       <c r="G42">
-        <v>-7.127744739631849</v>
+        <v>-7.698131872775039</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.055481697890594</v>
       </c>
       <c r="E43">
-        <v>-22.57858855866135</v>
+        <v>-24.27041286250498</v>
       </c>
       <c r="F43">
-        <v>-0.7577442587539387</v>
+        <v>-0.9091408271265904</v>
       </c>
       <c r="G43">
-        <v>-7.481122302130274</v>
+        <v>-6.628223144302298</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>2.255412259213314</v>
       </c>
       <c r="E44">
-        <v>-22.00000354859734</v>
+        <v>-23.05140200132821</v>
       </c>
       <c r="F44">
-        <v>-1.296412528344193</v>
+        <v>-1.082953017418997</v>
       </c>
       <c r="G44">
-        <v>-7.821254371926074</v>
+        <v>-7.066595652975971</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>2.438129102203355</v>
       </c>
       <c r="E45">
-        <v>-22.37916814878557</v>
+        <v>-22.79999923831838</v>
       </c>
       <c r="F45">
-        <v>-1.081327760574704</v>
+        <v>-0.9588660655818391</v>
       </c>
       <c r="G45">
-        <v>-8.492437685103454</v>
+        <v>-6.85460817991428</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>2.594004618814176</v>
       </c>
       <c r="E46">
-        <v>-22.71803838725355</v>
+        <v>-21.20196868812162</v>
       </c>
       <c r="F46">
-        <v>-1.198266730093105</v>
+        <v>-1.252136290664559</v>
       </c>
       <c r="G46">
-        <v>-7.711019826559422</v>
+        <v>-6.776403162640077</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>2.714018832012509</v>
       </c>
       <c r="E47">
-        <v>-21.31798819219814</v>
+        <v>-22.00443692465085</v>
       </c>
       <c r="F47">
-        <v>-0.879179606534735</v>
+        <v>-1.123055111755924</v>
       </c>
       <c r="G47">
-        <v>-7.666191729412151</v>
+        <v>-7.640250294566422</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>2.794017066765146</v>
       </c>
       <c r="E48">
-        <v>-21.38929807239693</v>
+        <v>-22.84827729971415</v>
       </c>
       <c r="F48">
-        <v>-1.17942551351643</v>
+        <v>-1.167477970465853</v>
       </c>
       <c r="G48">
-        <v>-6.944128641841712</v>
+        <v>-7.597699852750169</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>2.830402428264498</v>
       </c>
       <c r="E49">
-        <v>-20.65895936986187</v>
+        <v>-21.25927652668869</v>
       </c>
       <c r="F49">
-        <v>-1.256109969095788</v>
+        <v>-1.087364902206307</v>
       </c>
       <c r="G49">
-        <v>-8.365554406219806</v>
+        <v>-6.719590890640644</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>2.820279635335676</v>
       </c>
       <c r="E50">
-        <v>-19.39158440628318</v>
+        <v>-20.77123835440805</v>
       </c>
       <c r="F50">
-        <v>-1.700442102120429</v>
+        <v>-1.229171461156749</v>
       </c>
       <c r="G50">
-        <v>-6.856538227963675</v>
+        <v>-7.338172945744543</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>2.765713017997058</v>
       </c>
       <c r="E51">
-        <v>-20.78696121616268</v>
+        <v>-19.56362566230859</v>
       </c>
       <c r="F51">
-        <v>-1.329408887099905</v>
+        <v>-1.390855524304767</v>
       </c>
       <c r="G51">
-        <v>-8.079523271626776</v>
+        <v>-7.361363317247138</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>2.669658458580344</v>
       </c>
       <c r="E52">
-        <v>-18.46609564486159</v>
+        <v>-20.10749086215579</v>
       </c>
       <c r="F52">
-        <v>-1.51550907944544</v>
+        <v>-1.170891672532789</v>
       </c>
       <c r="G52">
-        <v>-8.963197260787815</v>
+        <v>-7.197795883242827</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>2.535719764250407</v>
       </c>
       <c r="E53">
-        <v>-18.92552744683578</v>
+        <v>-19.98751800027058</v>
       </c>
       <c r="F53">
-        <v>-1.476767992751312</v>
+        <v>-1.157214498345167</v>
       </c>
       <c r="G53">
-        <v>-8.490030918496403</v>
+        <v>-8.241816145598467</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>2.37073871709103</v>
       </c>
       <c r="E54">
-        <v>-18.95817321595707</v>
+        <v>-20.26912568491157</v>
       </c>
       <c r="F54">
-        <v>-1.640697759928321</v>
+        <v>-1.161334797806691</v>
       </c>
       <c r="G54">
-        <v>-9.5138998901545</v>
+        <v>-8.227468241231266</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>2.182791103825783</v>
       </c>
       <c r="E55">
-        <v>-18.46356875636531</v>
+        <v>-18.87627576352835</v>
       </c>
       <c r="F55">
-        <v>-0.7419398370759269</v>
+        <v>-1.311376985475766</v>
       </c>
       <c r="G55">
-        <v>-8.999993974456816</v>
+        <v>-8.370659267441363</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.978798976797536</v>
       </c>
       <c r="E56">
-        <v>-18.33572540665476</v>
+        <v>-19.20537808356179</v>
       </c>
       <c r="F56">
-        <v>-1.304343317858595</v>
+        <v>-1.401429634201503</v>
       </c>
       <c r="G56">
-        <v>-8.247900928299648</v>
+        <v>-8.183057272821943</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.765377858880577</v>
       </c>
       <c r="E57">
-        <v>-17.91887031730069</v>
+        <v>-18.27916476629896</v>
       </c>
       <c r="F57">
-        <v>-1.690760143916509</v>
+        <v>-0.9788148093760568</v>
       </c>
       <c r="G57">
-        <v>-9.357407091967611</v>
+        <v>-8.521530759302568</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.549936823776716</v>
       </c>
       <c r="E58">
-        <v>-17.4734858416983</v>
+        <v>-17.93503696950808</v>
       </c>
       <c r="F58">
-        <v>-0.7423987526170779</v>
+        <v>-1.371235642369461</v>
       </c>
       <c r="G58">
-        <v>-8.963614389525764</v>
+        <v>-9.223296892171735</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.336569794434758</v>
       </c>
       <c r="E59">
-        <v>-17.98709630670026</v>
+        <v>-18.43741681897101</v>
       </c>
       <c r="F59">
-        <v>-1.06843422195013</v>
+        <v>-1.494702147021922</v>
       </c>
       <c r="G59">
-        <v>-8.590204715969209</v>
+        <v>-8.392489004727317</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.126966706056469</v>
       </c>
       <c r="E60">
-        <v>-17.17556206520767</v>
+        <v>-18.15726277448648</v>
       </c>
       <c r="F60">
-        <v>-1.026440136465209</v>
+        <v>-1.213753058688441</v>
       </c>
       <c r="G60">
-        <v>-9.019714894234253</v>
+        <v>-8.322388202933249</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.9247752068285758</v>
       </c>
       <c r="E61">
-        <v>-17.47162011040714</v>
+        <v>-17.34579646010402</v>
       </c>
       <c r="F61">
-        <v>-1.67707220095265</v>
+        <v>-1.625440060736157</v>
       </c>
       <c r="G61">
-        <v>-10.03676745262699</v>
+        <v>-8.294943780412691</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.7299886499516812</v>
       </c>
       <c r="E62">
-        <v>-16.24560822841451</v>
+        <v>-17.54815132113677</v>
       </c>
       <c r="F62">
-        <v>-1.250126671345368</v>
+        <v>-1.728855104036452</v>
       </c>
       <c r="G62">
-        <v>-8.94282747408468</v>
+        <v>-9.225150797673727</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.5409001481928267</v>
       </c>
       <c r="E63">
-        <v>-17.16215325367096</v>
+        <v>-17.9998756603499</v>
       </c>
       <c r="F63">
-        <v>-1.555031316600407</v>
+        <v>-1.550996338981371</v>
       </c>
       <c r="G63">
-        <v>-9.087481761423135</v>
+        <v>-8.019499770454249</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.3575185946116248</v>
       </c>
       <c r="E64">
-        <v>-16.44673587299118</v>
+        <v>-17.29848749214588</v>
       </c>
       <c r="F64">
-        <v>-1.527261956156359</v>
+        <v>-1.282149698402791</v>
       </c>
       <c r="G64">
-        <v>-9.838856419198281</v>
+        <v>-8.748882474212017</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.1785108946356115</v>
       </c>
       <c r="E65">
-        <v>-17.69453877190872</v>
+        <v>-17.8039829317261</v>
       </c>
       <c r="F65">
-        <v>-1.484860313909261</v>
+        <v>-1.814690534314537</v>
       </c>
       <c r="G65">
-        <v>-9.027756209349144</v>
+        <v>-8.292010637064898</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.00164460916284409</v>
       </c>
       <c r="E66">
-        <v>-15.34883452067555</v>
+        <v>-17.68761020667698</v>
       </c>
       <c r="F66">
-        <v>-1.528207951730356</v>
+        <v>-1.472868039018932</v>
       </c>
       <c r="G66">
-        <v>-8.51039408410846</v>
+        <v>-8.291613371600185</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.1735025235100272</v>
       </c>
       <c r="E67">
-        <v>-16.84150559460985</v>
+        <v>-17.42430208550099</v>
       </c>
       <c r="F67">
-        <v>-1.631793638715629</v>
+        <v>-1.670211662122664</v>
       </c>
       <c r="G67">
-        <v>-8.754315079441961</v>
+        <v>-8.436449738943299</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.3463730966091558</v>
       </c>
       <c r="E68">
-        <v>-15.93498208233237</v>
+        <v>-17.64488858288862</v>
       </c>
       <c r="F68">
-        <v>-2.101693331627676</v>
+        <v>-1.611891283495968</v>
       </c>
       <c r="G68">
-        <v>-8.955222156583712</v>
+        <v>-8.392558526183642</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.5168878807690978</v>
       </c>
       <c r="E69">
-        <v>-16.68344826632013</v>
+        <v>-17.45401793193932</v>
       </c>
       <c r="F69">
-        <v>-1.564799425014219</v>
+        <v>-1.645105502878617</v>
       </c>
       <c r="G69">
-        <v>-9.362991982292362</v>
+        <v>-8.827994580963981</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.6834819378526393</v>
       </c>
       <c r="E70">
-        <v>-16.0400290938883</v>
+        <v>-16.27505236641238</v>
       </c>
       <c r="F70">
-        <v>-1.429843464484929</v>
+        <v>-1.641239512209751</v>
       </c>
       <c r="G70">
-        <v>-9.190956172798595</v>
+        <v>-8.815378091913818</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.8425669609930666</v>
       </c>
       <c r="E71">
-        <v>-16.85631823308893</v>
+        <v>-17.2594158184077</v>
       </c>
       <c r="F71">
-        <v>-1.699761184115328</v>
+        <v>-1.852858390765927</v>
       </c>
       <c r="G71">
-        <v>-8.705981114568601</v>
+        <v>-8.043521088887202</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.9913295088208454</v>
       </c>
       <c r="E72">
-        <v>-15.44176333578695</v>
+        <v>-18.1277552378525</v>
       </c>
       <c r="F72">
-        <v>-2.011085676742063</v>
+        <v>-1.584589122267099</v>
       </c>
       <c r="G72">
-        <v>-8.57058311255795</v>
+        <v>-8.734273036747213</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.126035861585701</v>
       </c>
       <c r="E73">
-        <v>-17.51279752455888</v>
+        <v>-18.29180373725437</v>
       </c>
       <c r="F73">
-        <v>-1.464240592518775</v>
+        <v>-1.698270122790289</v>
       </c>
       <c r="G73">
-        <v>-8.501290083875464</v>
+        <v>-8.044616879460701</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.241507296234256</v>
       </c>
       <c r="E74">
-        <v>-17.13269100177706</v>
+        <v>-17.17635907663302</v>
       </c>
       <c r="F74">
-        <v>-2.441095337372301</v>
+        <v>-1.944658066344168</v>
       </c>
       <c r="G74">
-        <v>-8.646086724672108</v>
+        <v>-7.5506801744559</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.333652796247146</v>
       </c>
       <c r="E75">
-        <v>-18.41924405277823</v>
+        <v>-18.4436117714135</v>
       </c>
       <c r="F75">
-        <v>-1.764661285022461</v>
+        <v>-2.085941097096041</v>
       </c>
       <c r="G75">
-        <v>-8.634701758562555</v>
+        <v>-7.758301037951293</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.398651356245551</v>
       </c>
       <c r="E76">
-        <v>-17.33808899734296</v>
+        <v>-18.94684750246389</v>
       </c>
       <c r="F76">
-        <v>-2.455348226904869</v>
+        <v>-2.111310677174179</v>
       </c>
       <c r="G76">
-        <v>-8.412120539775195</v>
+        <v>-8.207949264731724</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.432986815336105</v>
       </c>
       <c r="E77">
-        <v>-17.86905710321632</v>
+        <v>-19.17869631470859</v>
       </c>
       <c r="F77">
-        <v>-2.532141198613994</v>
+        <v>-2.430970202607882</v>
       </c>
       <c r="G77">
-        <v>-7.963051658464138</v>
+        <v>-7.940291657881648</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.434567491016693</v>
       </c>
       <c r="E78">
-        <v>-18.1585126333126</v>
+        <v>-19.44703557050711</v>
       </c>
       <c r="F78">
-        <v>-2.699258523556975</v>
+        <v>-2.280971090043753</v>
       </c>
       <c r="G78">
-        <v>-8.297092324467679</v>
+        <v>-8.020367133385539</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.402290644148663</v>
       </c>
       <c r="E79">
-        <v>-17.5038311460237</v>
+        <v>-19.7676107739841</v>
       </c>
       <c r="F79">
-        <v>-2.270565967097189</v>
+        <v>-2.853128596994386</v>
       </c>
       <c r="G79">
-        <v>-7.03984313447312</v>
+        <v>-7.593704024284269</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.336157029535894</v>
       </c>
       <c r="E80">
-        <v>-18.90706032983249</v>
+        <v>-19.01041369210956</v>
       </c>
       <c r="F80">
-        <v>-3.063309429739302</v>
+        <v>-2.37729365164128</v>
       </c>
       <c r="G80">
-        <v>-7.173387230981781</v>
+        <v>-6.909986985695208</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.238207480043511</v>
       </c>
       <c r="E81">
-        <v>-18.71373524597104</v>
+        <v>-20.2907536767722</v>
       </c>
       <c r="F81">
-        <v>-2.957225386667186</v>
+        <v>-2.698602456573958</v>
       </c>
       <c r="G81">
-        <v>-7.594789883221149</v>
+        <v>-7.086220566932771</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.111582373018427</v>
       </c>
       <c r="E82">
-        <v>-21.28433710184714</v>
+        <v>-21.74956535055115</v>
       </c>
       <c r="F82">
-        <v>-2.783148118805884</v>
+        <v>-2.775327502156054</v>
       </c>
       <c r="G82">
-        <v>-6.866685050041541</v>
+        <v>-7.743178465927902</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.9601665976784304</v>
       </c>
       <c r="E83">
-        <v>-21.33265591950898</v>
+        <v>-22.76506658982321</v>
       </c>
       <c r="F83">
-        <v>-3.489192163968792</v>
+        <v>-2.385892105282339</v>
       </c>
       <c r="G83">
-        <v>-6.772397402537559</v>
+        <v>-6.651218193618075</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.7894326823843</v>
       </c>
       <c r="E84">
-        <v>-20.77348447751585</v>
+        <v>-23.00307412671835</v>
       </c>
       <c r="F84">
-        <v>-2.799679847063554</v>
+        <v>-2.899319191741889</v>
       </c>
       <c r="G84">
-        <v>-6.506398379002658</v>
+        <v>-7.142148923273218</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.6059290580531804</v>
       </c>
       <c r="E85">
-        <v>-23.03222391390572</v>
+        <v>-22.95424811996765</v>
       </c>
       <c r="F85">
-        <v>-2.804486034734596</v>
+        <v>-2.665690591293331</v>
       </c>
       <c r="G85">
-        <v>-6.533942117889394</v>
+        <v>-7.320368831834343</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.4163749024373964</v>
       </c>
       <c r="E86">
-        <v>-23.78573934641203</v>
+        <v>-23.51659402224015</v>
       </c>
       <c r="F86">
-        <v>-2.847020215766142</v>
+        <v>-2.559358038000375</v>
       </c>
       <c r="G86">
-        <v>-7.780038079962147</v>
+        <v>-6.921573895082657</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.2276971103694564</v>
       </c>
       <c r="E87">
-        <v>-24.80864011221263</v>
+        <v>-24.20789727882909</v>
       </c>
       <c r="F87">
-        <v>-3.557119119365754</v>
+        <v>-2.834799311472641</v>
       </c>
       <c r="G87">
-        <v>-6.55204087035259</v>
+        <v>-6.607542166318471</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.04919638282661588</v>
       </c>
       <c r="E88">
-        <v>-24.22076720195889</v>
+        <v>-25.52363181633568</v>
       </c>
       <c r="F88">
-        <v>-3.418630171863525</v>
+        <v>-2.925813694753029</v>
       </c>
       <c r="G88">
-        <v>-6.796852402436155</v>
+        <v>-6.833450483372798</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.1103552923898494</v>
       </c>
       <c r="E89">
-        <v>-27.33098654906299</v>
+        <v>-26.84969127457977</v>
       </c>
       <c r="F89">
-        <v>-3.451433521014385</v>
+        <v>-2.925170053281053</v>
       </c>
       <c r="G89">
-        <v>-7.155669191255601</v>
+        <v>-6.496390599837441</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.2426832089318185</v>
       </c>
       <c r="E90">
-        <v>-28.069562545818</v>
+        <v>-28.00040369077286</v>
       </c>
       <c r="F90">
-        <v>-3.572597164287063</v>
+        <v>-3.009500339988252</v>
       </c>
       <c r="G90">
-        <v>-7.322633244983204</v>
+        <v>-7.417248636495575</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.3390293721250671</v>
       </c>
       <c r="E91">
-        <v>-30.46531096330993</v>
+        <v>-28.78813174440711</v>
       </c>
       <c r="F91">
-        <v>-3.916094618471129</v>
+        <v>-2.980466890887532</v>
       </c>
       <c r="G91">
-        <v>-6.742460139225929</v>
+        <v>-7.202380988814718</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.3911333472642546</v>
       </c>
       <c r="E92">
-        <v>-32.0129916752524</v>
+        <v>-31.9617451991446</v>
       </c>
       <c r="F92">
-        <v>-3.252650195364588</v>
+        <v>-3.062618571325367</v>
       </c>
       <c r="G92">
-        <v>-7.144393473148844</v>
+        <v>-7.399030704392966</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.3931370967492239</v>
       </c>
       <c r="E93">
-        <v>-32.88429045246122</v>
+        <v>-32.17529444792432</v>
       </c>
       <c r="F93">
-        <v>-3.147826927479533</v>
+        <v>-2.824211947697461</v>
       </c>
       <c r="G93">
-        <v>-8.313330550337804</v>
+        <v>-7.591999093331544</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.3430023248166905</v>
       </c>
       <c r="E94">
-        <v>-34.81978741418357</v>
+        <v>-34.33400215772175</v>
       </c>
       <c r="F94">
-        <v>-3.725512130109046</v>
+        <v>-3.238254826638738</v>
       </c>
       <c r="G94">
-        <v>-7.927029612451327</v>
+        <v>-7.456329626586672</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.2396634479483822</v>
       </c>
       <c r="E95">
-        <v>-35.9123112036151</v>
+        <v>-35.2353745308155</v>
       </c>
       <c r="F95">
-        <v>-2.803054615862559</v>
+        <v>-3.254473432018149</v>
       </c>
       <c r="G95">
-        <v>-8.276103465748699</v>
+        <v>-7.948452152635952</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.08417018495020225</v>
       </c>
       <c r="E96">
-        <v>-38.62316895645676</v>
+        <v>-37.2631165080741</v>
       </c>
       <c r="F96">
-        <v>-3.794646016811888</v>
+        <v>-3.03120108083939</v>
       </c>
       <c r="G96">
-        <v>-7.685320061538059</v>
+        <v>-7.694433993407673</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.1140626686300057</v>
       </c>
       <c r="E97">
-        <v>-38.27230052610546</v>
+        <v>-39.28000826161032</v>
       </c>
       <c r="F97">
-        <v>-4.095494146895417</v>
+        <v>-3.234762429668535</v>
       </c>
       <c r="G97">
-        <v>-9.242815868671279</v>
+        <v>-8.441011670696415</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.3521954591149527</v>
       </c>
       <c r="E98">
-        <v>-41.70365887170052</v>
+        <v>-41.21373232575868</v>
       </c>
       <c r="F98">
-        <v>-3.75286316501468</v>
+        <v>-3.392933386661281</v>
       </c>
       <c r="G98">
-        <v>-8.43153688936302</v>
+        <v>-8.560095304289538</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.6142274102460294</v>
       </c>
       <c r="E99">
-        <v>-43.51775423798824</v>
+        <v>-43.4167737960912</v>
       </c>
       <c r="F99">
-        <v>-4.197886156453256</v>
+        <v>-3.251764670610995</v>
       </c>
       <c r="G99">
-        <v>-9.126572683150849</v>
+        <v>-9.191667940089539</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.9035854075431222</v>
       </c>
       <c r="E100">
-        <v>-45.41768909332836</v>
+        <v>-45.96375286730629</v>
       </c>
       <c r="F100">
-        <v>-3.609302952272512</v>
+        <v>-3.47113872479218</v>
       </c>
       <c r="G100">
-        <v>-9.19470702089459</v>
+        <v>-9.327347338471029</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.192631490463714</v>
       </c>
       <c r="E101">
-        <v>-49.16832976307122</v>
+        <v>-46.68842871309475</v>
       </c>
       <c r="F101">
-        <v>-4.068232575669286</v>
+        <v>-3.306808856159619</v>
       </c>
       <c r="G101">
-        <v>-8.253035584431057</v>
+        <v>-9.548207073577966</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.510510540734652</v>
       </c>
       <c r="E102">
-        <v>-49.1195524374161</v>
+        <v>-49.15460961894648</v>
       </c>
       <c r="F102">
-        <v>-4.54717389878289</v>
+        <v>-3.37841624792722</v>
       </c>
       <c r="G102">
-        <v>-9.722593370404615</v>
+        <v>-9.465797663468889</v>
       </c>
     </row>
   </sheetData>
